--- a/reading/reading.xlsx
+++ b/reading/reading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkudija/Documents/GitHub/mkudija.github.io/reading/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E565F7-DC56-9344-AC5A-B808F31A504D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599ABD53-6B3A-7942-BADE-ACB2482654B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4713" uniqueCount="2294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4748" uniqueCount="2312">
   <si>
     <t>Title</t>
   </si>
@@ -6918,6 +6918,60 @@
   </si>
   <si>
     <t>This was one of the Cluny books we got recently, and I really enjoyed reading it to the boys. The stories are so well-written and pious, they stir you on to holiness.</t>
+  </si>
+  <si>
+    <t>The Holy Spirit</t>
+  </si>
+  <si>
+    <t>Luis M. Martínez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk to people! </t>
+  </si>
+  <si>
+    <t>Eat Your Ice Cream: Six Simple Rules for a Long and Healthy Life</t>
+  </si>
+  <si>
+    <t>Ezekiel J. Emanuel, MD</t>
+  </si>
+  <si>
+    <t>Black Fox of Lorne</t>
+  </si>
+  <si>
+    <t>A Song for Nagasaki</t>
+  </si>
+  <si>
+    <t>Paul Glynn</t>
+  </si>
+  <si>
+    <t>Ben-Hur</t>
+  </si>
+  <si>
+    <t>Lew Wallace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This was my lenten reading for 2026 which I finished about a week into Easter. I loved it! </t>
+  </si>
+  <si>
+    <t>This is very rich and I hope to come back and finish it, but I got bogged down after the first part and had to move on.</t>
+  </si>
+  <si>
+    <t>This was mom's book club pick, and we had a great discussion about it. I actually really liked her perspective and message based in scripture. I had forgotten I had listened to it already.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I had fun reading this to the boys! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This was our book club pick this year, and not well-written but very powerful to see God's providence in everything! </t>
+  </si>
+  <si>
+    <t>The Story of All Stories</t>
+  </si>
+  <si>
+    <t>Emily Stimpson Chapman</t>
+  </si>
+  <si>
+    <t>WOF Kid's Bible: short and sweet and we read it with Ruth.</t>
   </si>
 </sst>
 </file>
@@ -6927,11 +6981,25 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.0%;_(* \(#,##0.0\)%;_(* &quot;   -&quot;?_)"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7190,46 +7258,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -7251,10 +7321,10 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -51351,14 +51421,30 @@
       <c r="Z1060" s="3"/>
     </row>
     <row r="1061" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1061" s="3"/>
-      <c r="B1061" s="3"/>
-      <c r="C1061" s="3"/>
-      <c r="D1061" s="7"/>
-      <c r="E1061" s="7"/>
-      <c r="F1061" s="7"/>
-      <c r="G1061" s="6"/>
-      <c r="H1061" s="3"/>
+      <c r="A1061" s="3" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B1061" s="42" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C1061" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1061" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1061" s="7">
+        <v>1957</v>
+      </c>
+      <c r="F1061" s="7">
+        <v>296</v>
+      </c>
+      <c r="G1061" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="H1061" s="3" t="s">
+        <v>2305</v>
+      </c>
       <c r="I1061" s="3"/>
       <c r="J1061" s="3"/>
       <c r="K1061" s="3"/>
@@ -51379,14 +51465,30 @@
       <c r="Z1061" s="3"/>
     </row>
     <row r="1062" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1062" s="3"/>
-      <c r="B1062" s="3"/>
-      <c r="C1062" s="3"/>
-      <c r="D1062" s="7"/>
-      <c r="E1062" s="7"/>
-      <c r="F1062" s="7"/>
-      <c r="G1062" s="6"/>
-      <c r="H1062" s="3"/>
+      <c r="A1062" s="3" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B1062" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C1062" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1062" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1062" s="7">
+        <v>2015</v>
+      </c>
+      <c r="F1062" s="7">
+        <v>224</v>
+      </c>
+      <c r="G1062" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="H1062" s="3" t="s">
+        <v>2306</v>
+      </c>
       <c r="I1062" s="3"/>
       <c r="J1062" s="3"/>
       <c r="K1062" s="3"/>
@@ -51407,14 +51509,30 @@
       <c r="Z1062" s="3"/>
     </row>
     <row r="1063" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1063" s="3"/>
-      <c r="B1063" s="3"/>
-      <c r="C1063" s="3"/>
-      <c r="D1063" s="7"/>
-      <c r="E1063" s="7"/>
-      <c r="F1063" s="7"/>
-      <c r="G1063" s="6"/>
-      <c r="H1063" s="3"/>
+      <c r="A1063" s="3" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B1063" s="43" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C1063" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1063" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1063" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F1063" s="7">
+        <v>488</v>
+      </c>
+      <c r="G1063" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1063" s="3" t="s">
+        <v>2311</v>
+      </c>
       <c r="I1063" s="3"/>
       <c r="J1063" s="3"/>
       <c r="K1063" s="3"/>
@@ -51435,14 +51553,30 @@
       <c r="Z1063" s="3"/>
     </row>
     <row r="1064" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1064" s="3"/>
-      <c r="B1064" s="3"/>
-      <c r="C1064" s="3"/>
-      <c r="D1064" s="7"/>
-      <c r="E1064" s="7"/>
-      <c r="F1064" s="7"/>
-      <c r="G1064" s="6"/>
-      <c r="H1064" s="3"/>
+      <c r="A1064" s="3" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B1064" s="3" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C1064" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1064" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1064" s="7">
+        <v>2026</v>
+      </c>
+      <c r="F1064" s="7">
+        <v>167</v>
+      </c>
+      <c r="G1064" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="H1064" s="3" t="s">
+        <v>2296</v>
+      </c>
       <c r="I1064" s="3"/>
       <c r="J1064" s="3"/>
       <c r="K1064" s="3"/>
@@ -51463,14 +51597,30 @@
       <c r="Z1064" s="3"/>
     </row>
     <row r="1065" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1065" s="3"/>
-      <c r="B1065" s="3"/>
-      <c r="C1065" s="3"/>
-      <c r="D1065" s="7"/>
-      <c r="E1065" s="7"/>
-      <c r="F1065" s="7"/>
-      <c r="G1065" s="6"/>
-      <c r="H1065" s="3"/>
+      <c r="A1065" s="3" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B1065" s="3" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C1065" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1065" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1065" s="7">
+        <v>1957</v>
+      </c>
+      <c r="F1065" s="7">
+        <v>220</v>
+      </c>
+      <c r="G1065" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="H1065" s="3" t="s">
+        <v>2307</v>
+      </c>
       <c r="I1065" s="3"/>
       <c r="J1065" s="3"/>
       <c r="K1065" s="3"/>
@@ -51491,14 +51641,30 @@
       <c r="Z1065" s="3"/>
     </row>
     <row r="1066" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1066" s="3"/>
-      <c r="B1066" s="3"/>
-      <c r="C1066" s="3"/>
-      <c r="D1066" s="7"/>
-      <c r="E1066" s="7"/>
-      <c r="F1066" s="7"/>
-      <c r="G1066" s="6"/>
-      <c r="H1066" s="3"/>
+      <c r="A1066" s="3" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B1066" s="3" t="s">
+        <v>2301</v>
+      </c>
+      <c r="C1066" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1066" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1066" s="7">
+        <v>1988</v>
+      </c>
+      <c r="F1066" s="7">
+        <v>267</v>
+      </c>
+      <c r="G1066" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="H1066" s="3" t="s">
+        <v>2308</v>
+      </c>
       <c r="I1066" s="3"/>
       <c r="J1066" s="3"/>
       <c r="K1066" s="3"/>
@@ -51519,14 +51685,30 @@
       <c r="Z1066" s="3"/>
     </row>
     <row r="1067" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1067" s="3"/>
-      <c r="B1067" s="3"/>
-      <c r="C1067" s="3"/>
-      <c r="D1067" s="7"/>
-      <c r="E1067" s="7"/>
-      <c r="F1067" s="7"/>
-      <c r="G1067" s="6"/>
-      <c r="H1067" s="3"/>
+      <c r="A1067" s="3" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B1067" s="3" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C1067" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1067" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1067" s="7">
+        <v>1880</v>
+      </c>
+      <c r="F1067" s="7">
+        <v>575</v>
+      </c>
+      <c r="G1067" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="H1067" s="3" t="s">
+        <v>2304</v>
+      </c>
       <c r="I1067" s="3"/>
       <c r="J1067" s="3"/>
       <c r="K1067" s="3"/>
@@ -52836,17 +53018,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G812">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH(("Yes"),(G2))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G841:G842">
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH(("Yes"),(G841))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1009">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH(("Yes"),(G1009))))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/reading/reading.xlsx
+++ b/reading/reading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkudija/Documents/GitHub/mkudija.github.io/reading/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599ABD53-6B3A-7942-BADE-ACB2482654B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E836928A-B1B7-2348-A32F-195440F14690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14700" yWindow="740" windowWidth="14700" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Books" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4748" uniqueCount="2312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4772" uniqueCount="2320">
   <si>
     <t>Title</t>
   </si>
@@ -6972,6 +6972,30 @@
   </si>
   <si>
     <t>WOF Kid's Bible: short and sweet and we read it with Ruth.</t>
+  </si>
+  <si>
+    <t>The Power of Prayer: Building Blocks of Faith Series</t>
+  </si>
+  <si>
+    <t>Kindred</t>
+  </si>
+  <si>
+    <t>Octavia Butler</t>
+  </si>
+  <si>
+    <t>The Ecumenical Councils of the Catholic Church</t>
+  </si>
+  <si>
+    <t>Joseph F. Kelly</t>
+  </si>
+  <si>
+    <t>Myths of the Norsemen</t>
+  </si>
+  <si>
+    <t>The Restoration of Christian Culture</t>
+  </si>
+  <si>
+    <t>John Senior</t>
   </si>
 </sst>
 </file>
@@ -6981,11 +7005,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.0%;_(* \(#,##0.0\)%;_(* &quot;   -&quot;?_)"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7224,6 +7255,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -7258,46 +7295,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="1" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -7320,11 +7358,14 @@
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -51729,13 +51770,27 @@
       <c r="Z1067" s="3"/>
     </row>
     <row r="1068" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1068" s="3"/>
-      <c r="B1068" s="3"/>
-      <c r="C1068" s="3"/>
-      <c r="D1068" s="7"/>
-      <c r="E1068" s="7"/>
-      <c r="F1068" s="7"/>
-      <c r="G1068" s="6"/>
+      <c r="A1068" s="3" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B1068" s="3" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C1068" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1068" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1068" s="7">
+        <v>2026</v>
+      </c>
+      <c r="F1068" s="7">
+        <v>150</v>
+      </c>
+      <c r="G1068" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="H1068" s="3"/>
       <c r="I1068" s="3"/>
       <c r="J1068" s="3"/>
@@ -51757,13 +51812,27 @@
       <c r="Z1068" s="3"/>
     </row>
     <row r="1069" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1069" s="3"/>
-      <c r="B1069" s="3"/>
-      <c r="C1069" s="3"/>
-      <c r="D1069" s="7"/>
-      <c r="E1069" s="7"/>
-      <c r="F1069" s="7"/>
-      <c r="G1069" s="6"/>
+      <c r="A1069" s="3" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B1069" s="3" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C1069" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1069" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1069" s="7">
+        <v>1979</v>
+      </c>
+      <c r="F1069" s="7">
+        <v>292</v>
+      </c>
+      <c r="G1069" s="6" t="s">
+        <v>915</v>
+      </c>
       <c r="H1069" s="3"/>
       <c r="I1069" s="3"/>
       <c r="J1069" s="3"/>
@@ -51785,13 +51854,27 @@
       <c r="Z1069" s="3"/>
     </row>
     <row r="1070" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1070" s="3"/>
-      <c r="B1070" s="3"/>
-      <c r="C1070" s="3"/>
-      <c r="D1070" s="7"/>
-      <c r="E1070" s="7"/>
-      <c r="F1070" s="7"/>
-      <c r="G1070" s="6"/>
+      <c r="A1070" s="44" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1070" s="3" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C1070" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1070" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1070" s="7">
+        <v>2009</v>
+      </c>
+      <c r="F1070" s="7">
+        <v>236</v>
+      </c>
+      <c r="G1070" s="6" t="s">
+        <v>915</v>
+      </c>
       <c r="H1070" s="3"/>
       <c r="I1070" s="3"/>
       <c r="J1070" s="3"/>
@@ -51813,13 +51896,27 @@
       <c r="Z1070" s="3"/>
     </row>
     <row r="1071" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1071" s="3"/>
-      <c r="B1071" s="3"/>
-      <c r="C1071" s="3"/>
-      <c r="D1071" s="7"/>
-      <c r="E1071" s="7"/>
-      <c r="F1071" s="7"/>
-      <c r="G1071" s="6"/>
+      <c r="A1071" s="44" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B1071" s="3" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C1071" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1071" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1071" s="7">
+        <v>1962</v>
+      </c>
+      <c r="F1071" s="7">
+        <v>257</v>
+      </c>
+      <c r="G1071" s="6" t="s">
+        <v>915</v>
+      </c>
       <c r="H1071" s="3"/>
       <c r="I1071" s="3"/>
       <c r="J1071" s="3"/>
@@ -51841,13 +51938,27 @@
       <c r="Z1071" s="3"/>
     </row>
     <row r="1072" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1072" s="3"/>
-      <c r="B1072" s="3"/>
-      <c r="C1072" s="3"/>
-      <c r="D1072" s="7"/>
-      <c r="E1072" s="7"/>
-      <c r="F1072" s="7"/>
-      <c r="G1072" s="6"/>
+      <c r="A1072" s="44" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1072" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C1072" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1072" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1072" s="7">
+        <v>1968</v>
+      </c>
+      <c r="F1072" s="7">
+        <v>20</v>
+      </c>
+      <c r="G1072" s="6" t="s">
+        <v>915</v>
+      </c>
       <c r="H1072" s="3"/>
       <c r="I1072" s="3"/>
       <c r="J1072" s="3"/>
@@ -51869,13 +51980,27 @@
       <c r="Z1072" s="3"/>
     </row>
     <row r="1073" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1073" s="3"/>
-      <c r="B1073" s="3"/>
-      <c r="C1073" s="3"/>
-      <c r="D1073" s="7"/>
-      <c r="E1073" s="7"/>
-      <c r="F1073" s="7"/>
-      <c r="G1073" s="6"/>
+      <c r="A1073" s="44" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B1073" s="3" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C1073" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1073" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1073" s="7">
+        <v>1983</v>
+      </c>
+      <c r="F1073" s="7">
+        <v>142</v>
+      </c>
+      <c r="G1073" s="45" t="s">
+        <v>2089</v>
+      </c>
       <c r="H1073" s="3"/>
       <c r="I1073" s="3"/>
       <c r="J1073" s="3"/>

--- a/reading/reading.xlsx
+++ b/reading/reading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkudija/Documents/GitHub/mkudija.github.io/reading/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E836928A-B1B7-2348-A32F-195440F14690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19720CC6-C62E-8242-AE95-A048B6679870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14700" yWindow="740" windowWidth="14700" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4772" uniqueCount="2320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4782" uniqueCount="2325">
   <si>
     <t>Title</t>
   </si>
@@ -6996,6 +6996,21 @@
   </si>
   <si>
     <t>John Senior</t>
+  </si>
+  <si>
+    <t>Revenge of the Tipping Point</t>
+  </si>
+  <si>
+    <t>Kudija family book club, not that great.</t>
+  </si>
+  <si>
+    <t>Liftoff: Elon Musk and the Desperate Early Days That Launched SpaceX</t>
+  </si>
+  <si>
+    <t>Eric Berger</t>
+  </si>
+  <si>
+    <t>Remember what Elon went through to get where he is.</t>
   </si>
 </sst>
 </file>
@@ -7005,11 +7020,25 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.0%;_(* \(#,##0.0\)%;_(* &quot;   -&quot;?_)"/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7295,46 +7324,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -7356,16 +7387,16 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -51896,28 +51927,30 @@
       <c r="Z1070" s="3"/>
     </row>
     <row r="1071" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1071" s="44" t="s">
-        <v>2317</v>
+      <c r="A1071" s="46" t="s">
+        <v>2320</v>
       </c>
       <c r="B1071" s="3" t="s">
-        <v>2283</v>
+        <v>247</v>
       </c>
       <c r="C1071" s="3" t="s">
-        <v>10</v>
+        <v>244</v>
       </c>
       <c r="D1071" s="7">
         <v>2026</v>
       </c>
       <c r="E1071" s="7">
-        <v>1962</v>
+        <v>2024</v>
       </c>
       <c r="F1071" s="7">
-        <v>257</v>
+        <v>368</v>
       </c>
       <c r="G1071" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="H1071" s="3"/>
+      <c r="H1071" s="3" t="s">
+        <v>2321</v>
+      </c>
       <c r="I1071" s="3"/>
       <c r="J1071" s="3"/>
       <c r="K1071" s="3"/>
@@ -51939,10 +51972,10 @@
     </row>
     <row r="1072" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1072" s="44" t="s">
-        <v>541</v>
+        <v>2317</v>
       </c>
       <c r="B1072" s="3" t="s">
-        <v>542</v>
+        <v>2283</v>
       </c>
       <c r="C1072" s="3" t="s">
         <v>10</v>
@@ -51951,10 +51984,10 @@
         <v>2026</v>
       </c>
       <c r="E1072" s="7">
-        <v>1968</v>
+        <v>1962</v>
       </c>
       <c r="F1072" s="7">
-        <v>20</v>
+        <v>257</v>
       </c>
       <c r="G1072" s="6" t="s">
         <v>915</v>
@@ -51981,10 +52014,10 @@
     </row>
     <row r="1073" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1073" s="44" t="s">
-        <v>2318</v>
+        <v>541</v>
       </c>
       <c r="B1073" s="3" t="s">
-        <v>2319</v>
+        <v>542</v>
       </c>
       <c r="C1073" s="3" t="s">
         <v>10</v>
@@ -51993,13 +52026,13 @@
         <v>2026</v>
       </c>
       <c r="E1073" s="7">
-        <v>1983</v>
+        <v>1968</v>
       </c>
       <c r="F1073" s="7">
-        <v>142</v>
-      </c>
-      <c r="G1073" s="45" t="s">
-        <v>2089</v>
+        <v>20</v>
+      </c>
+      <c r="G1073" s="6" t="s">
+        <v>915</v>
       </c>
       <c r="H1073" s="3"/>
       <c r="I1073" s="3"/>
@@ -52022,13 +52055,27 @@
       <c r="Z1073" s="3"/>
     </row>
     <row r="1074" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1074" s="3"/>
-      <c r="B1074" s="3"/>
-      <c r="C1074" s="3"/>
-      <c r="D1074" s="7"/>
-      <c r="E1074" s="7"/>
-      <c r="F1074" s="7"/>
-      <c r="G1074" s="6"/>
+      <c r="A1074" s="44" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B1074" s="3" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C1074" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1074" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1074" s="7">
+        <v>1983</v>
+      </c>
+      <c r="F1074" s="7">
+        <v>142</v>
+      </c>
+      <c r="G1074" s="45" t="s">
+        <v>2089</v>
+      </c>
       <c r="H1074" s="3"/>
       <c r="I1074" s="3"/>
       <c r="J1074" s="3"/>
@@ -52050,14 +52097,30 @@
       <c r="Z1074" s="3"/>
     </row>
     <row r="1075" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1075" s="3"/>
-      <c r="B1075" s="3"/>
-      <c r="C1075" s="3"/>
-      <c r="D1075" s="7"/>
-      <c r="E1075" s="7"/>
-      <c r="F1075" s="7"/>
-      <c r="G1075" s="6"/>
-      <c r="H1075" s="3"/>
+      <c r="A1075" s="47" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1075" s="3" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1075" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1075" s="7">
+        <v>2026</v>
+      </c>
+      <c r="E1075" s="7">
+        <v>2021</v>
+      </c>
+      <c r="F1075" s="7">
+        <v>288</v>
+      </c>
+      <c r="G1075" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="H1075" s="3" t="s">
+        <v>2324</v>
+      </c>
       <c r="I1075" s="3"/>
       <c r="J1075" s="3"/>
       <c r="K1075" s="3"/>
